--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,522 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125581655</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bissandbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>557905</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7315970</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125581670</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79963</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bissandbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558101</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7315816</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125581658</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79932</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bissandbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7315823</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125581666</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91184</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bissandbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>558003</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7315930</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125581675</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5176</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bissandbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558050</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7315855</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125581658</v>
+        <v>125581675</v>
       </c>
       <c r="B6" t="n">
-        <v>79932</v>
+        <v>5176</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bissandbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558100</v>
+        <v>558050</v>
       </c>
       <c r="R6" t="n">
-        <v>7315823</v>
+        <v>7315855</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125581666</v>
+        <v>125581658</v>
       </c>
       <c r="B7" t="n">
-        <v>91184</v>
+        <v>79932</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558003</v>
+        <v>558100</v>
       </c>
       <c r="R7" t="n">
-        <v>7315930</v>
+        <v>7315823</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125581675</v>
+        <v>125581666</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>91184</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,43 +1344,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bissandbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558050</v>
+        <v>558003</v>
       </c>
       <c r="R8" t="n">
-        <v>7315855</v>
+        <v>7315930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -918,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125581655</v>
+        <v>125581666</v>
       </c>
       <c r="B4" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557905</v>
+        <v>558003</v>
       </c>
       <c r="R4" t="n">
-        <v>7315970</v>
+        <v>7315930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,37 +1015,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125581670</v>
+        <v>125581655</v>
       </c>
       <c r="B5" t="n">
-        <v>79963</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558101</v>
+        <v>557905</v>
       </c>
       <c r="R5" t="n">
-        <v>7315816</v>
+        <v>7315970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1094,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,11 +1117,6 @@
       <c r="B6" t="n">
         <v>5176</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1230,15 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125581658</v>
+        <v>125581670</v>
       </c>
       <c r="B7" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558100</v>
+        <v>558101</v>
       </c>
       <c r="R7" t="n">
-        <v>7315823</v>
+        <v>7315816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,6 +1293,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,37 +1312,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125581666</v>
+        <v>125581658</v>
       </c>
       <c r="B8" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558003</v>
+        <v>558100</v>
       </c>
       <c r="R8" t="n">
-        <v>7315930</v>
+        <v>7315823</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125581666</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125581666</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>125581655</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>125581670</v>
       </c>
       <c r="B7" t="n">
-        <v>80005</v>
+        <v>80006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>125581658</v>
       </c>
       <c r="B8" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125581666</v>
       </c>
       <c r="B4" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>125581655</v>
       </c>
       <c r="B5" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>125581670</v>
       </c>
       <c r="B7" t="n">
-        <v>80006</v>
+        <v>80010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>125581658</v>
       </c>
       <c r="B8" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125581666</v>
       </c>
       <c r="B4" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>125581655</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>125581670</v>
       </c>
       <c r="B7" t="n">
-        <v>80010</v>
+        <v>80011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>125581658</v>
       </c>
       <c r="B8" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125581666</v>
       </c>
       <c r="B4" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4723-2024 artfynd.xlsx
+++ b/artfynd/A 4723-2024 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125581666</v>
       </c>
       <c r="B4" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
